--- a/symbols_config.xlsx
+++ b/symbols_config.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>name</t>
   </si>
@@ -62,7 +62,7 @@
     <t>生猪</t>
   </si>
   <si>
-    <t>LH2603</t>
+    <t>LH2605</t>
   </si>
   <si>
     <t>焦煤</t>
@@ -92,7 +92,7 @@
     <t>鸡蛋</t>
   </si>
   <si>
-    <t>JD2603</t>
+    <t>JD2604</t>
   </si>
   <si>
     <t>红枣</t>
@@ -116,7 +116,7 @@
     <t>铜</t>
   </si>
   <si>
-    <t>CU2603</t>
+    <t>CU2604</t>
   </si>
   <si>
     <t>橡胶</t>
@@ -146,7 +146,7 @@
     <t>棉纱</t>
   </si>
   <si>
-    <t>CY2603</t>
+    <t>CY2605</t>
   </si>
   <si>
     <t>纸浆</t>
@@ -182,13 +182,13 @@
     <t>沪铅</t>
   </si>
   <si>
-    <t>PB2602</t>
+    <t>PB2604</t>
   </si>
   <si>
     <t>沥青</t>
   </si>
   <si>
-    <t>BU2603</t>
+    <t>BU2606</t>
   </si>
   <si>
     <t>燃油</t>
@@ -206,7 +206,7 @@
     <t>短纤</t>
   </si>
   <si>
-    <t>PF2602</t>
+    <t>PF2604</t>
   </si>
   <si>
     <t>玉米淀粉</t>
@@ -218,7 +218,7 @@
     <t>原木</t>
   </si>
   <si>
-    <t>LG2603</t>
+    <t>LG2605</t>
   </si>
   <si>
     <t>乙二醇</t>
@@ -303,18 +303,6 @@
   </si>
   <si>
     <t>SC2604</t>
-  </si>
-  <si>
-    <t>纤维板</t>
-  </si>
-  <si>
-    <t>FB2603</t>
-  </si>
-  <si>
-    <t>棕榈油</t>
-  </si>
-  <si>
-    <t>P2605</t>
   </si>
   <si>
     <t>聚丙烯</t>
@@ -1530,7 +1518,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -1962,22 +1950,6 @@
         <v>105</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>106</v>
-      </c>
-      <c r="B54" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>108</v>
-      </c>
-      <c r="B55" t="s">
-        <v>109</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/symbols_config.xlsx
+++ b/symbols_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="21390" windowHeight="9690"/>
   </bookViews>
   <sheets>
     <sheet name="symbols" sheetId="1" r:id="rId1"/>
@@ -176,7 +176,7 @@
     <t>合成橡胶</t>
   </si>
   <si>
-    <t>BR2604</t>
+    <t>BR2605</t>
   </si>
   <si>
     <t>沪铅</t>
@@ -296,13 +296,13 @@
     <t>沪镍</t>
   </si>
   <si>
-    <t>NI2603</t>
+    <t>NI2605</t>
   </si>
   <si>
     <t>原油</t>
   </si>
   <si>
-    <t>SC2604</t>
+    <t>SC2605</t>
   </si>
   <si>
     <t>聚丙烯</t>
